--- a/v4/03_extracted/SituationChap_VALIDATION_2024.xlsx
+++ b/v4/03_extracted/SituationChap_VALIDATION_2024.xlsx
@@ -1497,42 +1497,42 @@
         <v>875710.84</v>
       </c>
       <c r="M13" t="n">
-        <v>-1733333.33</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>297.9</v>
+        <v>100</v>
       </c>
       <c r="O13" t="n">
-        <v>-1733333.33</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>297.9</v>
+        <v>100</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1733333.33</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>297.9</v>
+        <v>100</v>
       </c>
       <c r="S13" t="n">
-        <v>-1457295.84</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>266.4</v>
+        <v>100</v>
       </c>
       <c r="U13" t="n">
-        <v>-1733333.33</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>297.9</v>
+        <v>100</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>naive</t>
+          <t>linear_trend</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>266.4</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -1761,42 +1761,42 @@
         <v>406663.2</v>
       </c>
       <c r="M16" t="n">
-        <v>-776854.03</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>291</v>
+        <v>100</v>
       </c>
       <c r="O16" t="n">
-        <v>-591709.52</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>245.5</v>
+        <v>100</v>
       </c>
       <c r="Q16" t="n">
-        <v>-622566.9399999999</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>253.1</v>
+        <v>100</v>
       </c>
       <c r="S16" t="n">
-        <v>-406232.47</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>199.9</v>
+        <v>100</v>
       </c>
       <c r="U16" t="n">
-        <v>-591709.51</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>245.5</v>
+        <v>100</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>naive</t>
+          <t>linear_trend</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>199.9</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -2013,42 +2013,42 @@
         <v>730612.75</v>
       </c>
       <c r="M19" t="n">
-        <v>-333333.33</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>145.6</v>
+        <v>100</v>
       </c>
       <c r="O19" t="n">
-        <v>-239755.88</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>132.8</v>
+        <v>100</v>
       </c>
       <c r="Q19" t="n">
-        <v>-280038.73</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>138.3</v>
+        <v>100</v>
       </c>
       <c r="S19" t="n">
-        <v>-333333.33</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>145.6</v>
+        <v>100</v>
       </c>
       <c r="U19" t="n">
-        <v>-333333.33</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>145.6</v>
+        <v>100</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>average</t>
+          <t>linear_trend</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>132.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20">
@@ -2617,42 +2617,42 @@
         <v>405144</v>
       </c>
       <c r="M26" t="n">
-        <v>-12733333.33</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3242.9</v>
+        <v>100</v>
       </c>
       <c r="O26" t="n">
-        <v>-5064242.19</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1350</v>
+        <v>100</v>
       </c>
       <c r="Q26" t="n">
-        <v>-7087557.68</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1849.4</v>
+        <v>100</v>
       </c>
       <c r="S26" t="n">
-        <v>-12493004.4</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>3183.6</v>
+        <v>100</v>
       </c>
       <c r="U26" t="n">
-        <v>-12493004.25</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>3183.6</v>
+        <v>100</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>average</t>
+          <t>linear_trend</t>
         </is>
       </c>
       <c r="X26" t="n">
-        <v>1350</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27">
@@ -4597,34 +4597,34 @@
         <v>12000</v>
       </c>
       <c r="M49" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
         <v>100</v>
       </c>
       <c r="O49" t="n">
-        <v>-16467.17</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>237.2</v>
+        <v>100</v>
       </c>
       <c r="Q49" t="n">
-        <v>-12055.44</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>200.5</v>
+        <v>100</v>
       </c>
       <c r="S49" t="n">
-        <v>-3232</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>126.9</v>
+        <v>100</v>
       </c>
       <c r="U49" t="n">
-        <v>-16467.17</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>237.2</v>
+        <v>100</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
@@ -5829,42 +5829,42 @@
         <v>3327536.88</v>
       </c>
       <c r="M63" t="n">
-        <v>-2001601.44</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>160.2</v>
+        <v>100</v>
       </c>
       <c r="O63" t="n">
-        <v>-2333333.33</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>170.1</v>
+        <v>100</v>
       </c>
       <c r="Q63" t="n">
-        <v>-2333333.33</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>170.1</v>
+        <v>100</v>
       </c>
       <c r="S63" t="n">
-        <v>-722900.65</v>
+        <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>121.7</v>
+        <v>100</v>
       </c>
       <c r="U63" t="n">
-        <v>-2333333.33</v>
+        <v>0</v>
       </c>
       <c r="V63" t="n">
-        <v>170.1</v>
+        <v>100</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>naive</t>
+          <t>linear_trend</t>
         </is>
       </c>
       <c r="X63" t="n">
-        <v>121.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="64">
@@ -8357,42 +8357,42 @@
         <v>457705.4</v>
       </c>
       <c r="M92" t="n">
-        <v>-2250877.33</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>591.8</v>
+        <v>100</v>
       </c>
       <c r="O92" t="n">
-        <v>-1161652.13</v>
+        <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>353.8</v>
+        <v>100</v>
       </c>
       <c r="Q92" t="n">
-        <v>-1378188.82</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>401.1</v>
+        <v>100</v>
       </c>
       <c r="S92" t="n">
-        <v>-1811262.21</v>
+        <v>0</v>
       </c>
       <c r="T92" t="n">
-        <v>495.7</v>
+        <v>100</v>
       </c>
       <c r="U92" t="n">
-        <v>-1162056.85</v>
+        <v>0</v>
       </c>
       <c r="V92" t="n">
-        <v>353.9</v>
+        <v>100</v>
       </c>
       <c r="W92" t="inlineStr">
         <is>
-          <t>average</t>
+          <t>linear_trend</t>
         </is>
       </c>
       <c r="X92" t="n">
-        <v>353.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="93">
@@ -9165,34 +9165,34 @@
         <v>24000</v>
       </c>
       <c r="M102" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
         <v>100</v>
       </c>
       <c r="O102" t="n">
-        <v>-1555578</v>
+        <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>6581.6</v>
+        <v>100</v>
       </c>
       <c r="Q102" t="n">
-        <v>-1555578</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>6581.6</v>
+        <v>100</v>
       </c>
       <c r="S102" t="n">
-        <v>-159545.26</v>
+        <v>0</v>
       </c>
       <c r="T102" t="n">
-        <v>764.8</v>
+        <v>100</v>
       </c>
       <c r="U102" t="n">
-        <v>-1555578</v>
+        <v>0</v>
       </c>
       <c r="V102" t="n">
-        <v>6581.6</v>
+        <v>100</v>
       </c>
       <c r="W102" t="inlineStr">
         <is>
@@ -9431,22 +9431,22 @@
       <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="n">
-        <v>-221689.33</v>
+        <v>0</v>
       </c>
       <c r="P105" t="n">
-        <v>128.2</v>
+        <v>100</v>
       </c>
       <c r="Q105" t="n">
-        <v>-221689.33</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>128.2</v>
+        <v>100</v>
       </c>
       <c r="S105" t="n">
-        <v>-221689.33</v>
+        <v>0</v>
       </c>
       <c r="T105" t="n">
-        <v>128.2</v>
+        <v>100</v>
       </c>
       <c r="U105" t="inlineStr"/>
       <c r="V105" t="inlineStr"/>
@@ -9456,7 +9456,7 @@
         </is>
       </c>
       <c r="X105" t="n">
-        <v>128.2</v>
+        <v>100</v>
       </c>
     </row>
     <row r="106">
@@ -10583,23 +10583,23 @@
         <v>875710.84</v>
       </c>
       <c r="M13" t="n">
-        <v>-1457295.84</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2295224.98</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>-2333006.68</v>
+        <v>-875710.84</v>
       </c>
       <c r="Q13" t="n">
-        <v>266.4</v>
+        <v>100</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>naive</t>
+          <t>linear_trend</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -10808,23 +10808,23 @@
         <v>406663.2</v>
       </c>
       <c r="M16" t="n">
-        <v>-406232.47</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>574591.4</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-812895.67</v>
+        <v>-406663.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>199.9</v>
+        <v>100</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>naive</t>
+          <t>linear_trend</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -11023,23 +11023,23 @@
         <v>730612.75</v>
       </c>
       <c r="M19" t="n">
-        <v>-239755.88</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>8367.25</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>-970368.63</v>
+        <v>-730612.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>132.8</v>
+        <v>100</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>average</t>
+          <t>linear_trend</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -11538,23 +11538,23 @@
         <v>405144</v>
       </c>
       <c r="M26" t="n">
-        <v>-5064242.19</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>7956263.3</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>-5469386.19</v>
+        <v>-405144</v>
       </c>
       <c r="Q26" t="n">
-        <v>1350</v>
+        <v>100</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>average</t>
+          <t>linear_trend</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -13243,13 +13243,13 @@
         <v>12000</v>
       </c>
       <c r="M49" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>37434.7</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
         <v>-12000</v>
@@ -14293,23 +14293,23 @@
         <v>3327536.88</v>
       </c>
       <c r="M63" t="n">
-        <v>-722900.65</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
         <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>8256084.98</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>-4050437.53</v>
+        <v>-3327536.88</v>
       </c>
       <c r="Q63" t="n">
-        <v>121.7</v>
+        <v>100</v>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>naive</t>
+          <t>linear_trend</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -16448,23 +16448,23 @@
         <v>457705.4</v>
       </c>
       <c r="M92" t="n">
-        <v>-1161652.13</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
         <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>675722.66</v>
+        <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>-1619357.53</v>
+        <v>-457705.4</v>
       </c>
       <c r="Q92" t="n">
-        <v>353.8</v>
+        <v>100</v>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>average</t>
+          <t>linear_trend</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -17160,13 +17160,13 @@
         <v>24000</v>
       </c>
       <c r="M102" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
         <v>0</v>
       </c>
       <c r="O102" t="n">
-        <v>7493663.19</v>
+        <v>0</v>
       </c>
       <c r="P102" t="n">
         <v>-24000</v>
@@ -17385,15 +17385,15 @@
         <v>786443.8</v>
       </c>
       <c r="M105" t="n">
-        <v>-221689.33</v>
+        <v>0</v>
       </c>
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="n">
-        <v>-1008133.13</v>
+        <v>-786443.8</v>
       </c>
       <c r="Q105" t="n">
-        <v>128.2</v>
+        <v>100</v>
       </c>
       <c r="R105" t="inlineStr">
         <is>
